--- a/examples/LargeDrugCombo_Goetz_Cancers_2024/tables/data__sa_fit_heat_GR__GR_Mean.xlsx
+++ b/examples/LargeDrugCombo_Goetz_Cancers_2024/tables/data__sa_fit_heat_GR__GR_Mean.xlsx
@@ -381,641 +381,641 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COLO 829</t>
+          <t>501A</t>
         </is>
       </c>
       <c r="B2">
-        <v>0.6530125985278624</v>
+        <v>0.8343635417303725</v>
       </c>
       <c r="C2">
-        <v>0.4474960760872611</v>
+        <v>0.8859666666666667</v>
       </c>
       <c r="D2">
-        <v>0.06071657776243643</v>
+        <v>0.5647834921180002</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK-MEL-28</t>
+          <t>624 mel</t>
         </is>
       </c>
       <c r="B3">
-        <v>0.6541700841220244</v>
+        <v>0.8942934501006347</v>
       </c>
       <c r="C3">
-        <v>0.6158798016748217</v>
+        <v>0.8897229078964952</v>
       </c>
       <c r="D3">
-        <v>0.2707560061967081</v>
+        <v>0.7254425098480141</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hs 695T</t>
+          <t>928 mel</t>
         </is>
       </c>
       <c r="B4">
-        <v>0.7608846644717628</v>
+        <v>0.7782924860452326</v>
       </c>
       <c r="C4">
-        <v>0.7341270589063742</v>
+        <v>0.7026177628510087</v>
       </c>
       <c r="D4">
-        <v>0.4844817070431627</v>
+        <v>0.4567204973541545</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MDA-MB-435</t>
+          <t>A-253</t>
         </is>
       </c>
       <c r="B5">
-        <v>0.8045767943241733</v>
+        <v>0.9857444444444444</v>
       </c>
       <c r="C5">
-        <v>0.8253077148420587</v>
+        <v>0.8915062965794005</v>
       </c>
       <c r="D5">
-        <v>0.5937412169201506</v>
+        <v>0.748027015287681</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>928 mel</t>
+          <t>A-375</t>
         </is>
       </c>
       <c r="B6">
-        <v>0.7782924860452326</v>
+        <v>0.7495538933448637</v>
       </c>
       <c r="C6">
-        <v>0.7026177628510087</v>
+        <v>0.7453622204611966</v>
       </c>
       <c r="D6">
-        <v>0.4567204973541545</v>
+        <v>0.5479607116530693</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>624 mel</t>
+          <t>A-431</t>
         </is>
       </c>
       <c r="B7">
-        <v>0.8942934501006347</v>
+        <v>0.9981444444444445</v>
       </c>
       <c r="C7">
-        <v>0.8897229078964952</v>
+        <v>0.9382546151213483</v>
       </c>
       <c r="D7">
-        <v>0.7254425098480141</v>
+        <v>0.7514668214840061</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RPMI-7951</t>
+          <t>A2058</t>
         </is>
       </c>
       <c r="B8">
-        <v>0.9720540092647654</v>
+        <v>0.9383537044756948</v>
       </c>
       <c r="C8">
-        <v>0.9270238929593989</v>
+        <v>0.9390679205093571</v>
       </c>
       <c r="D8">
-        <v>0.791427367385478</v>
+        <v>0.8481569100194224</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G-361</t>
+          <t>A388</t>
         </is>
       </c>
       <c r="B9">
-        <v>0.6560030190735704</v>
+        <v>0.9938982776999145</v>
       </c>
       <c r="C9">
-        <v>0.7325438314566614</v>
+        <v>0.8753700111042809</v>
       </c>
       <c r="D9">
-        <v>0.1709304326415744</v>
+        <v>0.7713441124547683</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hs 294T</t>
+          <t>COLO 800</t>
         </is>
       </c>
       <c r="B10">
-        <v>0.902621623763696</v>
+        <v>0.6935062569967324</v>
       </c>
       <c r="C10">
-        <v>0.8182380826239618</v>
+        <v>0.5050025257080013</v>
       </c>
       <c r="D10">
-        <v>0.6973586251223103</v>
+        <v>0.148035982491923</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A-431</t>
+          <t>COLO 829</t>
         </is>
       </c>
       <c r="B11">
-        <v>0.9981444444444445</v>
+        <v>0.6530125985278624</v>
       </c>
       <c r="C11">
-        <v>0.9382546151213483</v>
+        <v>0.4474960760872611</v>
       </c>
       <c r="D11">
-        <v>0.7514668214840061</v>
+        <v>0.06071657776243643</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A-375</t>
+          <t>COLO 849</t>
         </is>
       </c>
       <c r="B12">
-        <v>0.7495538933448637</v>
+        <v>0.8019367222147744</v>
       </c>
       <c r="C12">
-        <v>0.7453622204611966</v>
+        <v>0.6295919427586757</v>
       </c>
       <c r="D12">
-        <v>0.5479607116530693</v>
+        <v>0.3777480737993045</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>501A</t>
+          <t>COLO 857</t>
         </is>
       </c>
       <c r="B13">
-        <v>0.8343635417303725</v>
+        <v>0.6864641184753426</v>
       </c>
       <c r="C13">
-        <v>0.8859666666666667</v>
+        <v>0.6833121793388649</v>
       </c>
       <c r="D13">
-        <v>0.5647834921180002</v>
+        <v>0.3687561316003687</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK-MEL-2</t>
+          <t>G-361</t>
         </is>
       </c>
       <c r="B14">
-        <v>0.9892555555555556</v>
+        <v>0.6560030190735704</v>
       </c>
       <c r="C14">
-        <v>0.460457618634917</v>
+        <v>0.7325438314566614</v>
       </c>
       <c r="D14">
-        <v>0.2257721814632555</v>
+        <v>0.1709304326415744</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MEL-JUSO</t>
+          <t>HCC1498</t>
         </is>
       </c>
       <c r="B15">
-        <v>0.9987151204304261</v>
+        <v>0.7841088708140065</v>
       </c>
       <c r="C15">
-        <v>0.7052412669420323</v>
+        <v>0.5597191374867352</v>
       </c>
       <c r="D15">
-        <v>0.6147619266643939</v>
+        <v>0.4221861451846227</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK-MEL-30</t>
+          <t>HMY-1</t>
         </is>
       </c>
       <c r="B16">
-        <v>1.028122222222222</v>
+        <v>0.6328058952073933</v>
       </c>
       <c r="C16">
-        <v>0.5809580309368483</v>
+        <v>0.6067156376439045</v>
       </c>
       <c r="D16">
-        <v>0.4594279207874011</v>
+        <v>0.4256101119734457</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Hs 852.T</t>
+          <t>HSC-1</t>
         </is>
       </c>
       <c r="B17">
-        <v>1.004866666666667</v>
+        <v>0.9884555555555555</v>
       </c>
       <c r="C17">
-        <v>0.9014598784271027</v>
+        <v>0.9503078959742858</v>
       </c>
       <c r="D17">
-        <v>0.5103080298814987</v>
+        <v>0.8303789684941356</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COLO 800</t>
+          <t>HT-144</t>
         </is>
       </c>
       <c r="B18">
-        <v>0.6935062569967324</v>
+        <v>0.6587950317084283</v>
       </c>
       <c r="C18">
-        <v>0.5050025257080013</v>
+        <v>0.5729556179033872</v>
       </c>
       <c r="D18">
-        <v>0.148035982491923</v>
+        <v>0.2732425838632703</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SK-MEL-1</t>
+          <t>Hs 294T</t>
         </is>
       </c>
       <c r="B19">
-        <v>0.5529002410915723</v>
+        <v>0.902621623763696</v>
       </c>
       <c r="C19">
-        <v>0.4903211678531813</v>
+        <v>0.8182380826239618</v>
       </c>
       <c r="D19">
-        <v>-0.1544517246733309</v>
+        <v>0.6973586251223103</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UACC-62</t>
+          <t>Hs 695T</t>
         </is>
       </c>
       <c r="B20">
-        <v>0.5721200775541628</v>
+        <v>0.7608846644717628</v>
       </c>
       <c r="C20">
-        <v>0.5146846934339935</v>
+        <v>0.7341270589063742</v>
       </c>
       <c r="D20">
-        <v>0.2129268695546936</v>
+        <v>0.4844817070431627</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SK-MEL-24</t>
+          <t>Hs 852.T</t>
         </is>
       </c>
       <c r="B21">
-        <v>0.4503674458763403</v>
+        <v>1.004866666666667</v>
       </c>
       <c r="C21">
-        <v>0.3747340144215128</v>
+        <v>0.9014598784271027</v>
       </c>
       <c r="D21">
-        <v>-0.1383852094327119</v>
+        <v>0.5103080298814987</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COLO 849</t>
+          <t>IGR-1</t>
         </is>
       </c>
       <c r="B22">
-        <v>0.8019367222147744</v>
+        <v>0.9229942960126295</v>
       </c>
       <c r="C22">
-        <v>0.6295919427586757</v>
+        <v>0.9136725148731101</v>
       </c>
       <c r="D22">
-        <v>0.3777480737993045</v>
+        <v>0.7350749917618742</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A2058</t>
+          <t>IGR-39</t>
         </is>
       </c>
       <c r="B23">
-        <v>0.9383537044756948</v>
+        <v>0.9639829990816237</v>
       </c>
       <c r="C23">
-        <v>0.9390679205093571</v>
+        <v>0.955657737327673</v>
       </c>
       <c r="D23">
-        <v>0.8481569100194224</v>
+        <v>0.8739672232054294</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SK23-mel</t>
+          <t>MDA-MB-435</t>
         </is>
       </c>
       <c r="B24">
-        <v>0.9470760391473244</v>
+        <v>0.8045767943241733</v>
       </c>
       <c r="C24">
-        <v>0.6391807392870263</v>
+        <v>0.8253077148420587</v>
       </c>
       <c r="D24">
-        <v>0.5101227906973974</v>
+        <v>0.5937412169201506</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UCSD-242l</t>
+          <t>MEL-HO</t>
         </is>
       </c>
       <c r="B25">
-        <v>0.5257972971604714</v>
+        <v>0.7215091240698819</v>
       </c>
       <c r="C25">
-        <v>0.4667989196032913</v>
+        <v>0.6261948334046371</v>
       </c>
       <c r="D25">
-        <v>0.2996106762109565</v>
+        <v>0.2964262457942001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MEL-HO</t>
+          <t>MEL-JUSO</t>
         </is>
       </c>
       <c r="B26">
-        <v>0.7215091240698819</v>
+        <v>0.9987151204304261</v>
       </c>
       <c r="C26">
-        <v>0.6261948334046371</v>
+        <v>0.7052412669420323</v>
       </c>
       <c r="D26">
-        <v>0.2964262457942001</v>
+        <v>0.6147619266643939</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WM-266-4</t>
+          <t>MMAc</t>
         </is>
       </c>
       <c r="B27">
-        <v>0.7014520277896165</v>
+        <v>0.5068033985144035</v>
       </c>
       <c r="C27">
-        <v>0.4829211046615213</v>
+        <v>0.314842330464946</v>
       </c>
       <c r="D27">
-        <v>0.1782322210983967</v>
+        <v>-0.05972621074549509</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IGR-1</t>
+          <t>RPMI-7951</t>
         </is>
       </c>
       <c r="B28">
-        <v>0.9229942960126295</v>
+        <v>0.9720540092647654</v>
       </c>
       <c r="C28">
-        <v>0.9136725148731101</v>
+        <v>0.9270238929593989</v>
       </c>
       <c r="D28">
-        <v>0.7350749917618742</v>
+        <v>0.791427367385478</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IGR-39</t>
+          <t>RVH-421</t>
         </is>
       </c>
       <c r="B29">
-        <v>0.9639829990816237</v>
+        <v>0.50617749318699</v>
       </c>
       <c r="C29">
-        <v>0.955657737327673</v>
+        <v>0.5453159861673232</v>
       </c>
       <c r="D29">
-        <v>0.8739672232054294</v>
+        <v>0.1307870903714404</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COLO 857</t>
+          <t>SK-MEL-1</t>
         </is>
       </c>
       <c r="B30">
-        <v>0.6864641184753426</v>
+        <v>0.5529002410915723</v>
       </c>
       <c r="C30">
-        <v>0.6833121793388649</v>
+        <v>0.4903211678531813</v>
       </c>
       <c r="D30">
-        <v>0.3687561316003687</v>
+        <v>-0.1544517246733309</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HMY-1</t>
+          <t>SK-MEL-2</t>
         </is>
       </c>
       <c r="B31">
-        <v>0.6328058952073933</v>
+        <v>0.9892555555555556</v>
       </c>
       <c r="C31">
-        <v>0.6067156376439045</v>
+        <v>0.460457618634917</v>
       </c>
       <c r="D31">
-        <v>0.4256101119734457</v>
+        <v>0.2257721814632555</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MMAc</t>
+          <t>SK-MEL-24</t>
         </is>
       </c>
       <c r="B32">
-        <v>0.5068033985144035</v>
+        <v>0.4503674458763403</v>
       </c>
       <c r="C32">
-        <v>0.314842330464946</v>
+        <v>0.3747340144215128</v>
       </c>
       <c r="D32">
-        <v>-0.05972621074549509</v>
+        <v>-0.1383852094327119</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SK-MEL-3</t>
+          <t>SK-MEL-28</t>
         </is>
       </c>
       <c r="B33">
-        <v>0.6809819073314486</v>
+        <v>0.6541700841220244</v>
       </c>
       <c r="C33">
-        <v>0.6203792330478124</v>
+        <v>0.6158798016748217</v>
       </c>
       <c r="D33">
-        <v>0.3864929415268832</v>
+        <v>0.2707560061967081</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RVH-421</t>
+          <t>SK-MEL-3</t>
         </is>
       </c>
       <c r="B34">
-        <v>0.50617749318699</v>
+        <v>0.6809819073314486</v>
       </c>
       <c r="C34">
-        <v>0.5453159861673232</v>
+        <v>0.6203792330478124</v>
       </c>
       <c r="D34">
-        <v>0.1307870903714404</v>
+        <v>0.3864929415268832</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HSC-1</t>
+          <t>SK-MEL-30</t>
         </is>
       </c>
       <c r="B35">
-        <v>0.9884555555555555</v>
+        <v>1.028122222222222</v>
       </c>
       <c r="C35">
-        <v>0.9503078959742858</v>
+        <v>0.5809580309368483</v>
       </c>
       <c r="D35">
-        <v>0.8303789684941356</v>
+        <v>0.4594279207874011</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>UACC-257</t>
+          <t>SK-MEL-31</t>
         </is>
       </c>
       <c r="B36">
-        <v>0.712717764299059</v>
+        <v>0.8859553143053107</v>
       </c>
       <c r="C36">
-        <v>0.6292308303151462</v>
+        <v>0.835820601767862</v>
       </c>
       <c r="D36">
-        <v>0.3923394203917087</v>
+        <v>0.5783358680552154</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SK-MEL-31</t>
+          <t>SK23-mel</t>
         </is>
       </c>
       <c r="B37">
-        <v>0.8859553143053107</v>
+        <v>0.9470760391473244</v>
       </c>
       <c r="C37">
-        <v>0.835820601767862</v>
+        <v>0.6391807392870263</v>
       </c>
       <c r="D37">
-        <v>0.5783358680552154</v>
+        <v>0.5101227906973974</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HCC1498</t>
+          <t>UACC-257</t>
         </is>
       </c>
       <c r="B38">
-        <v>0.7841088708140065</v>
+        <v>0.712717764299059</v>
       </c>
       <c r="C38">
-        <v>0.5597191374867352</v>
+        <v>0.6292308303151462</v>
       </c>
       <c r="D38">
-        <v>0.4221861451846227</v>
+        <v>0.3923394203917087</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A-253</t>
+          <t>UACC-62</t>
         </is>
       </c>
       <c r="B39">
-        <v>0.9857444444444444</v>
+        <v>0.5721200775541628</v>
       </c>
       <c r="C39">
-        <v>0.8915062965794005</v>
+        <v>0.5146846934339935</v>
       </c>
       <c r="D39">
-        <v>0.748027015287681</v>
+        <v>0.2129268695546936</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HT-144</t>
+          <t>UCSD-242l</t>
         </is>
       </c>
       <c r="B40">
-        <v>0.6587950317084283</v>
+        <v>0.5257972971604714</v>
       </c>
       <c r="C40">
-        <v>0.5729556179033872</v>
+        <v>0.4667989196032913</v>
       </c>
       <c r="D40">
-        <v>0.2732425838632703</v>
+        <v>0.2996106762109565</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A388</t>
+          <t>WM-266-4</t>
         </is>
       </c>
       <c r="B41">
-        <v>0.9938982776999145</v>
+        <v>0.7014520277896165</v>
       </c>
       <c r="C41">
-        <v>0.8753700111042809</v>
+        <v>0.4829211046615213</v>
       </c>
       <c r="D41">
-        <v>0.7713441124547683</v>
+        <v>0.1782322210983967</v>
       </c>
     </row>
   </sheetData>
@@ -1043,7 +1043,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COLO 829</t>
+          <t>501A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1055,7 +1055,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK-MEL-28</t>
+          <t>624 mel</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1067,7 +1067,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hs 695T</t>
+          <t>928 mel</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1079,7 +1079,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MDA-MB-435</t>
+          <t>A-253</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1091,7 +1091,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>928 mel</t>
+          <t>A-375</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1103,7 +1103,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>624 mel</t>
+          <t>A-431</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1115,7 +1115,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RPMI-7951</t>
+          <t>A2058</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1127,7 +1127,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G-361</t>
+          <t>A388</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1139,7 +1139,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hs 294T</t>
+          <t>COLO 800</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1151,7 +1151,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A-431</t>
+          <t>COLO 829</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1163,7 +1163,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A-375</t>
+          <t>COLO 849</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,7 +1175,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>501A</t>
+          <t>COLO 857</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1187,7 +1187,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK-MEL-2</t>
+          <t>G-361</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1199,7 +1199,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MEL-JUSO</t>
+          <t>HCC1498</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK-MEL-30</t>
+          <t>HMY-1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1223,7 +1223,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Hs 852.T</t>
+          <t>HSC-1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1235,7 +1235,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COLO 800</t>
+          <t>HT-144</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SK-MEL-1</t>
+          <t>Hs 294T</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1259,7 +1259,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UACC-62</t>
+          <t>Hs 695T</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1271,7 +1271,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SK-MEL-24</t>
+          <t>Hs 852.T</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1283,7 +1283,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COLO 849</t>
+          <t>IGR-1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A2058</t>
+          <t>IGR-39</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1307,7 +1307,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SK23-mel</t>
+          <t>MDA-MB-435</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1319,7 +1319,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UCSD-242l</t>
+          <t>MEL-HO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1331,7 +1331,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MEL-HO</t>
+          <t>MEL-JUSO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WM-266-4</t>
+          <t>MMAc</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1355,7 +1355,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IGR-1</t>
+          <t>RPMI-7951</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IGR-39</t>
+          <t>RVH-421</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1379,7 +1379,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COLO 857</t>
+          <t>SK-MEL-1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1391,7 +1391,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HMY-1</t>
+          <t>SK-MEL-2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1403,7 +1403,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MMAc</t>
+          <t>SK-MEL-24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SK-MEL-3</t>
+          <t>SK-MEL-28</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1427,7 +1427,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RVH-421</t>
+          <t>SK-MEL-3</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1439,7 +1439,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HSC-1</t>
+          <t>SK-MEL-30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1451,7 +1451,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>UACC-257</t>
+          <t>SK-MEL-31</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1463,7 +1463,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SK-MEL-31</t>
+          <t>SK23-mel</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1475,7 +1475,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HCC1498</t>
+          <t>UACC-257</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A-253</t>
+          <t>UACC-62</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HT-144</t>
+          <t>UCSD-242l</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1511,7 +1511,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A388</t>
+          <t>WM-266-4</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
